--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/CALIFORNIA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/CALIFORNIA_2021.xlsx
@@ -607,7 +607,7 @@
         <v>1681</v>
       </c>
       <c r="D14">
-        <v>0.009180625112641519</v>
+        <v>0.009180625112641521</v>
       </c>
     </row>
     <row r="15">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C250">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C406">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C416">
@@ -11137,7 +11137,7 @@
         <v>178</v>
       </c>
       <c r="D599">
-        <v>0.0009721304402440157</v>
+        <v>0.0009721304402440156</v>
       </c>
     </row>
     <row r="600">
@@ -12469,7 +12469,7 @@
         <v>167</v>
       </c>
       <c r="D673">
-        <v>0.0009120549635997225</v>
+        <v>0.0009120549635997224</v>
       </c>
     </row>
     <row r="674">
@@ -12685,7 +12685,7 @@
         <v>168</v>
       </c>
       <c r="D685">
-        <v>0.0009175163705673855</v>
+        <v>0.0009175163705673856</v>
       </c>
     </row>
     <row r="686">
@@ -14557,7 +14557,7 @@
         <v>1827</v>
       </c>
       <c r="D789">
-        <v>0.009977990529920319</v>
+        <v>0.00997799052992032</v>
       </c>
     </row>
     <row r="790">
@@ -19014,7 +19014,7 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>San Bartolome Yucane</t>
+          <t>San Bartolome Yucuane</t>
         </is>
       </c>
       <c r="C1037">
@@ -19795,7 +19795,7 @@
         <v>168</v>
       </c>
       <c r="D1080">
-        <v>0.0009175163705673855</v>
+        <v>0.0009175163705673856</v>
       </c>
     </row>
     <row r="1081">
@@ -20544,7 +20544,7 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1122">
@@ -20562,7 +20562,7 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1123">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1221">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1222">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1235">
@@ -22675,7 +22675,7 @@
         <v>167</v>
       </c>
       <c r="D1240">
-        <v>0.0009120549635997225</v>
+        <v>0.0009120549635997224</v>
       </c>
     </row>
     <row r="1241">
@@ -25674,7 +25674,7 @@
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1407">
@@ -26689,7 +26689,7 @@
         <v>178</v>
       </c>
       <c r="D1463">
-        <v>0.0009721304402440157</v>
+        <v>0.0009721304402440156</v>
       </c>
     </row>
     <row r="1464">
@@ -31909,7 +31909,7 @@
         <v>168</v>
       </c>
       <c r="D1753">
-        <v>0.0009175163705673855</v>
+        <v>0.0009175163705673856</v>
       </c>
     </row>
     <row r="1754">
@@ -34908,7 +34908,7 @@
       </c>
       <c r="B1920" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1920">
